--- a/data/trans_camb/P1432-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1432-Estudios-trans_camb.xlsx
@@ -631,27 +631,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,24</t>
+          <t>-2,06; 0,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,24</t>
+          <t>-2,09; 0,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,83</t>
+          <t>-1,06; 2,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,82</t>
+          <t>-1,5; 1,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,82</t>
+          <t>-1,13; 0,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-70,13; 17,64</t>
+          <t>-69,87; 26,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-68,13; 20,75</t>
+          <t>-70,48; 28,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 73,6</t>
+          <t>-26,62; 83,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-35,77; 72,22</t>
+          <t>-39,72; 68,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,76; 34,68</t>
+          <t>-35,16; 34,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 36,62</t>
+          <t>-38,54; 36,39</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,55</t>
+          <t>-0,32; 0,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,18</t>
+          <t>-0,51; 0,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,3</t>
+          <t>-0,66; 0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,78</t>
+          <t>-0,29; 0,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,3</t>
+          <t>-0,36; 0,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,37</t>
+          <t>-0,3; 0,34</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-65,44; 307,71</t>
+          <t>-66,43; 320,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-88,05; 161,63</t>
+          <t>-86,42; 154,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,16; 141,25</t>
+          <t>-78,77; 110,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 269,32</t>
+          <t>-39,61; 258,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-60,29; 104,02</t>
+          <t>-60,59; 102,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,35; 126,87</t>
+          <t>-49,12; 114,83</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,18</t>
+          <t>-2,13; -0,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,02</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,07</t>
+          <t>0,21; 2,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,45</t>
+          <t>-0,72; 0,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,34</t>
+          <t>-0,75; 0,4</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 398,19</t>
+          <t>-100,0; 400,59</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,02</t>
+          <t>-0,91; 0,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; -0,17</t>
+          <t>-1,03; -0,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,76</t>
+          <t>-0,5; 0,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,56</t>
+          <t>-0,64; 0,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,25</t>
+          <t>-0,52; 0,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,08</t>
+          <t>-0,65; 0,09</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 7,8</t>
+          <t>-66,96; 12,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,44; -17,49</t>
+          <t>-73,47; -19,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,95; 63,92</t>
+          <t>-28,4; 60,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,31; 44,99</t>
+          <t>-38,07; 50,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,6; 22,4</t>
+          <t>-35,04; 21,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,86; 8,59</t>
+          <t>-43,24; 8,7</t>
         </is>
       </c>
     </row>
